--- a/output/pdf_financials_xlsx/OVAT.xlsx
+++ b/output/pdf_financials_xlsx/OVAT.xlsx
@@ -1906,13 +1906,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.462422</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.466243</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.618422</v>
       </c>
     </row>
     <row r="93">
@@ -3084,7 +3084,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="n">
         <v>1.462422</v>
       </c>

--- a/output/pdf_financials_xlsx/OVAT.xlsx
+++ b/output/pdf_financials_xlsx/OVAT.xlsx
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.048849</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.003312</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.072292</v>
       </c>
     </row>
     <row r="35">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.048849</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.003312</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.072292</v>
       </c>
     </row>
     <row r="37">
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.052367</v>
+        <v>0.003518</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.003312</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.072292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">

--- a/output/pdf_financials_xlsx/OVAT.xlsx
+++ b/output/pdf_financials_xlsx/OVAT.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.297202</v>
+        <v>0.571793</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.179579</v>
+        <v>0.479456</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.139192</v>
+        <v>0.441257</v>
       </c>
     </row>
     <row r="8">
@@ -1500,13 +1500,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.018641</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.005131</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.044961</v>
       </c>
     </row>
     <row r="68">
@@ -4604,7 +4604,11 @@
           <t>Management and director fees 11</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E65" s="5" t="n">
         <v>0.274591</v>
       </c>
